--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488161_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488161_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. PINILLA NUNEZ</t>
+          <t>J. RICARDO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2858</v>
+        <v>1.0435</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8774</v>
+        <v>1.8829</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5915</v>
+        <v>-0.8395</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.2108</v>
+        <v>-3.8196</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.4012</v>
+        <v>0.383</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1904</v>
+        <v>-4.2026</v>
       </c>
       <c r="J2" t="n">
-        <v>1.792</v>
+        <v>0.3911</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.8421</v>
+        <v>1.4681</v>
       </c>
       <c r="L2" t="n">
-        <v>2.6341</v>
+        <v>-1.077</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.0028</v>
+        <v>-4.2107</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.5591</v>
+        <v>-1.0851</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.4437</v>
+        <v>-3.1255</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.6676</v>
+        <v>1.4823</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.7057</v>
+        <v>-1.8529</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0382</v>
+        <v>3.3352</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0103</v>
+        <v>-0.0808</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7000999999999999</v>
+        <v>-0.1169</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3101</v>
+        <v>0.036</v>
       </c>
       <c r="V2" t="n">
-        <v>4.154</v>
+        <v>3.4616</v>
       </c>
       <c r="W2" t="n">
-        <v>4.091</v>
+        <v>3.4616</v>
       </c>
       <c r="X2" t="n">
-        <v>0.063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. MOLINA LOPEZ</t>
+          <t>J. PINILLA NUNEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1627</v>
+        <v>0.3601</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0659</v>
+        <v>2.1487</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9031</v>
+        <v>-1.7885</v>
       </c>
       <c r="G4" t="n">
-        <v>0.298</v>
+        <v>-2.2108</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8478</v>
+        <v>-3.4012</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5498</v>
+        <v>1.1904</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3942</v>
+        <v>1.792</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3527</v>
+        <v>-0.8421</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0415</v>
+        <v>2.6341</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0961</v>
+        <v>-4.0028</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5048</v>
+        <v>-2.5591</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5913</v>
+        <v>-1.4437</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5558999999999999</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5558999999999999</v>
+        <v>2.0382</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6912</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3283</v>
+        <v>-0.0286</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3629</v>
+        <v>0.1131</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>4.154</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>4.091</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. GARRIDO SOTO</t>
+          <t>M. MOLINA LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1936</v>
+        <v>0.1874</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0064</v>
+        <v>1.0659</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1872</v>
+        <v>-0.8784999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1557</v>
+        <v>0.298</v>
       </c>
       <c r="H5" t="n">
-        <v>1.46</v>
+        <v>0.8478</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6157</v>
+        <v>-0.5498</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2306</v>
+        <v>1.3942</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4426</v>
+        <v>1.3527</v>
       </c>
       <c r="L5" t="n">
-        <v>0.788</v>
+        <v>0.0415</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3863</v>
+        <v>-1.0961</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0174</v>
+        <v>-0.5048</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.4037</v>
+        <v>-0.5913</v>
       </c>
       <c r="P5" t="n">
         <v>0.5558999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4087</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3512</v>
+        <v>-0.6665</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5609</v>
+        <v>-0.3283</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2097</v>
+        <v>-0.3383</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.945</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.945</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. RICARDO</t>
+          <t>A. GALLEGO CONTRERAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3095</v>
+        <v>-0.1011</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6531</v>
+        <v>-0.5415</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9626</v>
+        <v>0.4405</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.8196</v>
+        <v>-1.0032</v>
       </c>
       <c r="H6" t="n">
-        <v>0.383</v>
+        <v>-1.4548</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.2026</v>
+        <v>0.4517</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3911</v>
+        <v>-0.484</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4681</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.077</v>
+        <v>0.0829</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.2107</v>
+        <v>-0.5191</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0851</v>
+        <v>-0.8878</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.1255</v>
+        <v>0.3687</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4823</v>
+        <v>1.1117</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.3352</v>
+        <v>1.1117</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4338</v>
+        <v>-0.2726</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3467</v>
+        <v>-0.0575</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0871</v>
+        <v>-0.2151</v>
       </c>
       <c r="V6" t="n">
-        <v>3.4616</v>
+        <v>0.063</v>
       </c>
       <c r="W6" t="n">
-        <v>3.4616</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GALLEGO CONTRERAS</t>
+          <t>F. GARRIDO SOTO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7439</v>
+        <v>-0.315</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0859</v>
+        <v>-0.3002</v>
       </c>
       <c r="F7" t="n">
-        <v>0.342</v>
+        <v>-0.0148</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0032</v>
+        <v>-0.1557</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4548</v>
+        <v>1.46</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4517</v>
+        <v>-1.6157</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.484</v>
+        <v>2.2306</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5669999999999999</v>
+        <v>1.4426</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0829</v>
+        <v>0.788</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5191</v>
+        <v>-2.3863</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8878</v>
+        <v>0.0174</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3687</v>
+        <v>-2.4037</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1117</v>
+        <v>2.4087</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9155</v>
+        <v>0.2298</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6019</v>
+        <v>0.2671</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3136</v>
+        <v>-0.0373</v>
       </c>
       <c r="V7" t="n">
-        <v>0.063</v>
+        <v>-0.945</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.945</v>
       </c>
       <c r="X7" t="n">
-        <v>0.063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1226</v>
+        <v>-1.5586</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.032</v>
+        <v>-0.6403</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0906</v>
+        <v>-0.9183</v>
       </c>
       <c r="G8" t="n">
         <v>-3.9723</v>
@@ -1078,13 +1078,13 @@
         <v>1.8529</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3251</v>
+        <v>-0.761</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.526</v>
+        <v>-0.1343</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7991</v>
+        <v>-0.6268</v>
       </c>
       <c r="V8" t="n">
         <v>1.3218</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6778</v>
+        <v>-4.0943</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0921</v>
+        <v>-4.1146</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4143</v>
+        <v>0.0203</v>
       </c>
       <c r="G9" t="n">
         <v>-3.7422</v>
@@ -1156,13 +1156,13 @@
         <v>2.0382</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6684</v>
+        <v>1.2519</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7571</v>
+        <v>0.7346</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9112</v>
+        <v>0.5173</v>
       </c>
       <c r="V9" t="n">
         <v>0.0635</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.3819</v>
+        <v>-4.2735</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.512</v>
+        <v>-3.5759</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8699</v>
+        <v>-0.6976</v>
       </c>
       <c r="G10" t="n">
         <v>-4.1933</v>
@@ -1234,13 +1234,13 @@
         <v>2.2234</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3251</v>
+        <v>-0.2167</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2584</v>
+        <v>-0.3224</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0667</v>
+        <v>0.1057</v>
       </c>
       <c r="V10" t="n">
         <v>0.6924</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.3835</v>
+        <v>-10.3393</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.8664</v>
+        <v>-7.6498</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5171</v>
+        <v>-2.6895</v>
       </c>
       <c r="G11" t="n">
         <v>-4.7702</v>
@@ -1312,13 +1312,13 @@
         <v>2.9646</v>
       </c>
       <c r="S11" t="n">
-        <v>0.778</v>
+        <v>-0.1778</v>
       </c>
       <c r="T11" t="n">
-        <v>0.776</v>
+        <v>-0.0074</v>
       </c>
       <c r="U11" t="n">
-        <v>0.002</v>
+        <v>-0.1704</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9444</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-18.7422</v>
+        <v>-18.4687</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.3763</v>
+        <v>-11.1027</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.3657</v>
+        <v>-7.3659</v>
       </c>
       <c r="G12" t="n">
         <v>-22.9472</v>
@@ -1363,13 +1363,13 @@
         <v>-13.517</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7041</v>
+        <v>1.704100000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8990000000000002</v>
+        <v>0.899</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8051000000000001</v>
+        <v>0.8051000000000004</v>
       </c>
       <c r="M12" t="n">
         <v>-24.6512</v>
@@ -1381,7 +1381,7 @@
         <v>-14.3221</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.7793</v>
+        <v>-2.779300000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-21.308</v>
@@ -1390,10 +1390,10 @@
         <v>18.5288</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8827999999999998</v>
+        <v>-0.6091</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2671999999999999</v>
+        <v>0.006300000000000045</v>
       </c>
       <c r="U12" t="n">
         <v>-0.6158</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. FREIRE DELTIO</t>
+          <t>H. ANDRADE CORREIA E SILVA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.9424</v>
+        <v>8.094900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0945</v>
+        <v>5.1336</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8479</v>
+        <v>2.9614</v>
       </c>
       <c r="G13" t="n">
-        <v>4.8366</v>
+        <v>10.6807</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5924</v>
+        <v>4.632</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2442</v>
+        <v>6.0487</v>
       </c>
       <c r="J13" t="n">
-        <v>5.3171</v>
+        <v>10.4012</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9579</v>
+        <v>4.5217</v>
       </c>
       <c r="L13" t="n">
-        <v>3.3592</v>
+        <v>5.8795</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4805</v>
+        <v>0.2795</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3656</v>
+        <v>0.1103</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.115</v>
+        <v>0.1692</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2234</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-4.6322</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2234</v>
+        <v>3.7057</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2524</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.148</v>
+        <v>-0.3205</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1044</v>
+        <v>0.235</v>
       </c>
       <c r="V13" t="n">
-        <v>0.63</v>
+        <v>-1.5738</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6294</v>
+        <v>-0.315</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0005</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H. ANDRADE CORREIA E SILVA</t>
+          <t>R. FREIRE DELTIO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.6041</v>
+        <v>7.7466</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8398</v>
+        <v>5.8987</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7644</v>
+        <v>1.8479</v>
       </c>
       <c r="G14" t="n">
-        <v>10.6807</v>
+        <v>4.8366</v>
       </c>
       <c r="H14" t="n">
-        <v>4.632</v>
+        <v>1.5924</v>
       </c>
       <c r="I14" t="n">
-        <v>6.0487</v>
+        <v>3.2442</v>
       </c>
       <c r="J14" t="n">
-        <v>10.4012</v>
+        <v>5.3171</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5217</v>
+        <v>1.9579</v>
       </c>
       <c r="L14" t="n">
-        <v>5.8795</v>
+        <v>3.3592</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2795</v>
+        <v>-0.4805</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1103</v>
+        <v>-0.3656</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1692</v>
+        <v>-0.115</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9264</v>
+        <v>2.2234</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.6322</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.7057</v>
+        <v>2.2234</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5763</v>
+        <v>0.0566</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6143</v>
+        <v>-0.0479</v>
       </c>
       <c r="U14" t="n">
-        <v>0.038</v>
+        <v>0.1044</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.5738</v>
+        <v>0.63</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.315</v>
+        <v>0.6294</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2589</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.3496</v>
+        <v>5.1612</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8293</v>
+        <v>3.6335</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5203</v>
+        <v>1.5277</v>
       </c>
       <c r="G15" t="n">
         <v>3.6385</v>
@@ -1624,13 +1624,13 @@
         <v>2.7793</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8021</v>
+        <v>0.6137</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6367</v>
+        <v>0.4409</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1654</v>
+        <v>0.1728</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9439</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0075</v>
+        <v>2.5956</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5353</v>
+        <v>1.025</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4721</v>
+        <v>1.5706</v>
       </c>
       <c r="G16" t="n">
         <v>2.4259</v>
@@ -1702,13 +1702,13 @@
         <v>2.2234</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4566</v>
+        <v>0.1315</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4713</v>
+        <v>0.0184</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0147</v>
+        <v>0.1131</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2589</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ÁLVAREZ RICO</t>
+          <t>G. GIL VARGAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9678</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.6109</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.3569</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.7962</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3221</v>
+        <v>0.6656</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6221</v>
+        <v>0.1306</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.6656</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3221</v>
+        <v>0.6656</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6221</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.1306</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.1306</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.0137</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.0547</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. GIL VARGAS</t>
+          <t>A. ÁLVAREZ RICO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9432</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6109</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3323</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7962</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6656</v>
+        <v>0.3221</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1306</v>
+        <v>0.6221</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6656</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6656</v>
+        <v>0.3221</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.6221</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1306</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1306</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0383</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0547</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0164</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. VIDAL</t>
+          <t>J. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3448</v>
+        <v>-0.1657</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9017</v>
+        <v>-2.5681</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2465</v>
+        <v>2.4024</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.0028</v>
+        <v>0.9056</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.5452</v>
+        <v>0.5061</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5424</v>
+        <v>0.3995</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.2822</v>
+        <v>1.0321</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.6555</v>
+        <v>0.6482</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3732</v>
+        <v>0.3839</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2795</v>
+        <v>-0.1265</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1103</v>
+        <v>-0.1421</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1692</v>
+        <v>0.0156</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R20" t="n">
-        <v>3.5205</v>
+        <v>3.7057</v>
       </c>
       <c r="S20" t="n">
-        <v>1.05</v>
+        <v>-0.1088</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2896</v>
+        <v>-0.1909</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2395</v>
+        <v>0.082</v>
       </c>
       <c r="V20" t="n">
-        <v>0.63</v>
+        <v>-1.8888</v>
       </c>
       <c r="W20" t="n">
-        <v>0.9439</v>
+        <v>-0.63</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3139</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.285</v>
       </c>
       <c r="E21" t="n">
         <v>-1.3296</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2416</v>
+        <v>1.0446</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3185</v>
@@ -2092,13 +2092,13 @@
         <v>1.1117</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0453</v>
+        <v>-0.1517</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2524</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2977</v>
+        <v>0.1007</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. LATORRE SANCHEZ</t>
+          <t>B. VIDAL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.613</v>
+        <v>-0.3315</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1556</v>
+        <v>-3.881</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5427</v>
+        <v>3.5494</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9056</v>
+        <v>-3.0028</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5061</v>
+        <v>-3.5452</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3995</v>
+        <v>0.5424</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0321</v>
+        <v>-3.2822</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6482</v>
+        <v>-3.6555</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3839</v>
+        <v>0.3732</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1265</v>
+        <v>0.2795</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1421</v>
+        <v>0.1103</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0156</v>
+        <v>0.1692</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R22" t="n">
-        <v>3.7057</v>
+        <v>3.5205</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5561</v>
+        <v>0.3737</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7784</v>
+        <v>0.3103</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2223</v>
+        <v>0.0634</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8888</v>
+        <v>0.63</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.63</v>
+        <v>0.9439</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2589</v>
+        <v>-0.3139</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8642</v>
+        <v>-1.2479</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9848</v>
+        <v>0.4951</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.849</v>
+        <v>-1.743</v>
       </c>
       <c r="G23" t="n">
         <v>1.4478</v>
@@ -2248,13 +2248,13 @@
         <v>0.7411</v>
       </c>
       <c r="S23" t="n">
-        <v>0.67</v>
+        <v>0.2863</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9986</v>
+        <v>0.5089</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3286</v>
+        <v>-0.2226</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9439</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.4192</v>
+        <v>-2.1495</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2013</v>
+        <v>-2.0055</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2179</v>
+        <v>-0.144</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6937</v>
@@ -2326,13 +2326,13 @@
         <v>0.1853</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0157</v>
+        <v>0.2854</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0336</v>
+        <v>0.1623</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0492</v>
+        <v>0.1231</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9974</v>
+        <v>-3.5238</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.473</v>
+        <v>-2.1792</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5244</v>
+        <v>-1.3446</v>
       </c>
       <c r="G25" t="n">
         <v>0.6985</v>
@@ -2404,13 +2404,13 @@
         <v>0.9264</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3253</v>
+        <v>0.1483</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2524</v>
+        <v>0.0414</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.07290000000000001</v>
+        <v>0.1069</v>
       </c>
       <c r="V25" t="n">
         <v>-2.5177</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>18.7422</v>
+        <v>19.3951</v>
       </c>
       <c r="E26" t="n">
-        <v>7.365800000000001</v>
+        <v>7.3658</v>
       </c>
       <c r="F26" t="n">
-        <v>11.3765</v>
+        <v>12.0293</v>
       </c>
       <c r="G26" t="n">
         <v>22.9472</v>
       </c>
       <c r="H26" t="n">
-        <v>9.429999999999998</v>
+        <v>9.43</v>
       </c>
       <c r="I26" t="n">
         <v>13.5172</v>
@@ -2470,7 +2470,7 @@
         <v>-0.8992</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.8048000000000001</v>
+        <v>-0.8047999999999998</v>
       </c>
       <c r="P26" t="n">
         <v>2.779299999999999</v>
@@ -2482,13 +2482,13 @@
         <v>21.3078</v>
       </c>
       <c r="S26" t="n">
-        <v>0.8829</v>
+        <v>1.5358</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6158000000000003</v>
+        <v>0.6158</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2670999999999999</v>
+        <v>0.9198</v>
       </c>
       <c r="V26" t="n">
         <v>-7.867000000000001</v>
@@ -2497,7 +2497,7 @@
         <v>0.6276999999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-8.494999999999999</v>
+        <v>-8.495000000000001</v>
       </c>
     </row>
   </sheetData>
